--- a/public/excel-converter/examples/41_타회사세줄_열순서변경.xlsx
+++ b/public/excel-converter/examples/41_타회사세줄_열순서변경.xlsx
@@ -4,6 +4,9 @@
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변형양식" sheetId="1" r:id="R4a9c6142f3604000"/>
   </x:sheets>
+  <x:definedNames>
+    <x:definedName name="_xlnm.Print_Area" localSheetId="0">'변형양식'!$A$1:$I$21</x:definedName>
+  </x:definedNames>
 </x:workbook>
 </file>
 
@@ -270,6 +273,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:pageSetUpPr fitToPage="1"/>
+  </x:sheetPr>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
@@ -592,5 +598,6 @@
     <x:mergeCell ref="A21:I21"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </x:worksheet>
 </file>